--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_magallanes_y_la_antartica_chilena.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>24.90216964736222</v>
+      </c>
+      <c r="C2">
         <v>32.39221842238045</v>
-      </c>
-      <c r="C2">
-        <v>24.90216964736222</v>
       </c>
       <c r="D2">
         <v>3.087161203226141</v>
       </c>
       <c r="E2">
-        <v>20.59337196951876</v>
+        <v>15.83156904257822</v>
       </c>
       <c r="F2">
         <v>63.57505898790303</v>
       </c>
       <c r="G2">
-        <v>15.83156904257822</v>
+        <v>20.59337196951876</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>20.49180327868853</v>
+      </c>
+      <c r="C3">
         <v>36.88524590163934</v>
-      </c>
-      <c r="C3">
-        <v>20.49180327868853</v>
       </c>
       <c r="D3">
         <v>2.711111111111111</v>
       </c>
       <c r="E3">
-        <v>23.4375</v>
+        <v>13.02083333333333</v>
       </c>
       <c r="F3">
         <v>63.54166666666666</v>
       </c>
       <c r="G3">
-        <v>13.02083333333333</v>
+        <v>23.4375</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>19.09090909090909</v>
+      </c>
+      <c r="C4">
         <v>26.36363636363636</v>
-      </c>
-      <c r="C4">
-        <v>19.09090909090909</v>
       </c>
       <c r="D4">
         <v>3.793103448275862</v>
       </c>
       <c r="E4">
-        <v>18.125</v>
+        <v>13.125</v>
       </c>
       <c r="F4">
         <v>68.75000000000001</v>
       </c>
       <c r="G4">
-        <v>13.125</v>
+        <v>18.125</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>30.96774193548387</v>
+      </c>
+      <c r="C5">
         <v>28.38709677419355</v>
-      </c>
-      <c r="C5">
-        <v>30.96774193548387</v>
       </c>
       <c r="D5">
         <v>3.522727272727273</v>
       </c>
       <c r="E5">
-        <v>17.81376518218623</v>
+        <v>19.4331983805668</v>
       </c>
       <c r="F5">
         <v>62.75303643724697</v>
       </c>
       <c r="G5">
-        <v>19.4331983805668</v>
+        <v>17.81376518218623</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>33.25242718446602</v>
+      </c>
+      <c r="C6">
         <v>12.37864077669903</v>
-      </c>
-      <c r="C6">
-        <v>33.25242718446602</v>
       </c>
       <c r="D6">
         <v>8.078431372549019</v>
       </c>
       <c r="E6">
-        <v>8.5</v>
+        <v>22.83333333333334</v>
       </c>
       <c r="F6">
         <v>68.66666666666666</v>
       </c>
       <c r="G6">
-        <v>22.83333333333334</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>26.82528574760905</v>
+      </c>
+      <c r="C7">
         <v>27.8049918357826</v>
-      </c>
-      <c r="C7">
-        <v>26.82528574760905</v>
       </c>
       <c r="D7">
         <v>3.596476510067114</v>
       </c>
       <c r="E7">
-        <v>17.98159601749887</v>
+        <v>17.34801629205008</v>
       </c>
       <c r="F7">
         <v>64.67038769045105</v>
       </c>
       <c r="G7">
-        <v>17.34801629205008</v>
+        <v>17.98159601749887</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>32.09876543209877</v>
+      </c>
+      <c r="C8">
         <v>33.64197530864197</v>
-      </c>
-      <c r="C8">
-        <v>32.09876543209877</v>
       </c>
       <c r="D8">
         <v>2.972477064220183</v>
       </c>
       <c r="E8">
-        <v>20.29795158286779</v>
+        <v>19.36685288640596</v>
       </c>
       <c r="F8">
         <v>60.33519553072626</v>
       </c>
       <c r="G8">
-        <v>19.36685288640596</v>
+        <v>20.29795158286779</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>28.04878048780488</v>
+      </c>
+      <c r="C9">
         <v>23.17073170731707</v>
-      </c>
-      <c r="C9">
-        <v>28.04878048780488</v>
       </c>
       <c r="D9">
         <v>4.315789473684211</v>
       </c>
       <c r="E9">
+        <v>18.54838709677419</v>
+      </c>
+      <c r="F9">
+        <v>66.1290322580645</v>
+      </c>
+      <c r="G9">
         <v>15.32258064516129</v>
-      </c>
-      <c r="F9">
-        <v>66.12903225806451</v>
-      </c>
-      <c r="G9">
-        <v>18.5483870967742</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>24.45259725133939</v>
+      </c>
+      <c r="C10">
         <v>30.53226182157</v>
-      </c>
-      <c r="C10">
-        <v>24.45259725133939</v>
       </c>
       <c r="D10">
         <v>3.275224108334923</v>
       </c>
       <c r="E10">
-        <v>19.70015781167806</v>
+        <v>15.77741038551138</v>
       </c>
       <c r="F10">
         <v>64.52243180281054</v>
       </c>
       <c r="G10">
-        <v>15.77741038551138</v>
+        <v>19.70015781167806</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>19.40298507462687</v>
+      </c>
+      <c r="C11">
         <v>13.43283582089552</v>
-      </c>
-      <c r="C11">
-        <v>19.40298507462687</v>
       </c>
       <c r="D11">
         <v>7.444444444444445</v>
       </c>
       <c r="E11">
+        <v>14.60674157303371</v>
+      </c>
+      <c r="F11">
+        <v>75.28089887640449</v>
+      </c>
+      <c r="G11">
         <v>10.1123595505618</v>
-      </c>
-      <c r="F11">
-        <v>75.28089887640451</v>
-      </c>
-      <c r="G11">
-        <v>14.60674157303371</v>
       </c>
     </row>
   </sheetData>
